--- a/output/laminas_comunales/comunal_o_ocup_a_2021_atacama.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_atacama.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>43.3063748810657</v>
+        <v>61.9715175789942</v>
       </c>
     </row>
     <row r="3">
@@ -399,22 +399,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>42.3156959226584</v>
+        <v>60.0918533993219</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3103</t>
+          <t>3304</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tierra Amarilla</t>
+          <t>Huasco</t>
         </is>
       </c>
       <c r="C4">
-        <v>37.1856660437363</v>
+        <v>56.6904761904762</v>
       </c>
     </row>
     <row r="5">
@@ -429,82 +429,892 @@
         </is>
       </c>
       <c r="C5">
-        <v>35.7589385213784</v>
+        <v>56.0647723800794</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Huasco</t>
+          <t>Diego de Almagro</t>
         </is>
       </c>
       <c r="C6">
-        <v>35.6424190250726</v>
+        <v>55.5685358255452</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chañaral</t>
+          <t>Diego de Almagro</t>
         </is>
       </c>
       <c r="C7">
-        <v>35.3388196915777</v>
+        <v>54.7601430509311</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3201</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Freirina</t>
+          <t>Chañaral</t>
         </is>
       </c>
       <c r="C8">
-        <v>33.0041256923251</v>
+        <v>53.6395147313692</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caldera</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="C9">
-        <v>32.2232966678754</v>
+        <v>52.1624555141572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>51.6328828828829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>51.1935708096476</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>50.0366434591425</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>49.0394600207684</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>48.5555768127033</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>3302</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Alto del Carmen</t>
         </is>
       </c>
-      <c r="C10">
+      <c r="C15">
+        <v>46.7450765864333</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.6958301355846</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>45.4978652028057</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>44.8761555904413</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>44.5271574303832</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>44.260677808728</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>44.1850461442202</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>43.7257900101937</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>43.3063748810657</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>42.3156959226584</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>41.9858038956751</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>40.6951191302336</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>38.2149901380671</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>38.1055529882933</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>37.1856660437363</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>35.7589385213784</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>35.6424190250726</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>35.5694237613266</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>35.3388196915777</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>34.592811883245</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>34.3137254901961</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>33.7660790852787</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>33.2263410591991</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>33.0041256923251</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>32.2232966678754</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>31.5314358538658</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>31.2141440137258</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>31.1748955067921</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>30.9064136125654</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>30.735326325011</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>30.7056319580878</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>29.0909090909091</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>28.2843137254902</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C48">
         <v>27.9514757378689</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>26.8358869304198</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>26.6066545123063</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>26.0143740902475</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>25.7699619771863</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>25.1551956815115</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>23.5215522249332</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>21.5244865718799</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>3202</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Diego de Almagro</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>17.4684542586751</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Copiapó</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>13.7043781916491</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Tierra Amarilla</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>12.6127369777287</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Chañaral</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>10.9833024118738</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Caldera</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>10.4739652870494</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Huasco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>10.1569126378287</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Vallenar</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>9.060738316057471</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>3303</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Freirina</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>8.54037267080745</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Alto del Carmen</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>7.50069386622259</v>
       </c>
     </row>
   </sheetData>
